--- a/diseases/d163/2010-2014.xlsx
+++ b/diseases/d163/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2101,9 +2092,6 @@
       <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -2497,9 +2485,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2893,9 +2878,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -3289,9 +3271,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -3685,9 +3664,6 @@
       <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -4081,9 +4057,6 @@
       <c r="O19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -4477,9 +4450,6 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -4873,9 +4843,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -5269,9 +5236,6 @@
       <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -5665,9 +5629,6 @@
       <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -6061,9 +6022,6 @@
       <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1009495720545741</v>
       </c>
@@ -6457,9 +6415,6 @@
       <c r="O31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.04037982882182966</v>
       </c>
@@ -6853,9 +6808,6 @@
       <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.08075965764365932</v>
       </c>
@@ -7249,9 +7201,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -7645,9 +7594,6 @@
       <c r="O37" t="n">
         <v>5</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1009495720545741</v>
       </c>
@@ -8041,9 +7987,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -8437,9 +8380,6 @@
       <c r="O41" t="n">
         <v>4</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.08075965764365932</v>
       </c>
@@ -8833,9 +8773,6 @@
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.08075965764365932</v>
       </c>
@@ -9229,9 +9166,6 @@
       <c r="O45" t="n">
         <v>3</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -9625,9 +9559,6 @@
       <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.08075965764365932</v>
       </c>
@@ -10021,9 +9952,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -10417,9 +10345,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -10813,9 +10738,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -11209,9 +11131,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -11605,9 +11524,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -12001,9 +11917,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -12397,9 +12310,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12941,9 +12851,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -13337,9 +13244,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -13733,9 +13637,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -14129,9 +14030,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -14525,9 +14423,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -14921,9 +14816,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -15317,9 +15209,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -15713,9 +15602,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.05905367083031134</v>
       </c>
@@ -16109,9 +15995,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16505,9 +16388,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16901,9 +16781,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17297,9 +17174,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -17693,9 +17567,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -18089,9 +17960,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -18485,9 +18353,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18881,9 +18746,6 @@
       <c r="O94" t="n">
         <v>4</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -19277,9 +19139,6 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1377918986040598</v>
       </c>
@@ -19673,9 +19532,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -20069,9 +19925,6 @@
       <c r="O100" t="n">
         <v>4</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -20465,9 +20318,6 @@
       <c r="O102" t="n">
         <v>4</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -21009,9 +20859,6 @@
       <c r="O105" t="n">
         <v>4</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -21405,9 +21252,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -21801,9 +21645,6 @@
       <c r="O109" t="n">
         <v>3</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.05839535406563053</v>
       </c>
@@ -22197,9 +22038,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -22593,9 +22431,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -22989,9 +22824,6 @@
       <c r="O115" t="n">
         <v>4</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -23385,9 +23217,6 @@
       <c r="O117" t="n">
         <v>4</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -23781,9 +23610,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -24177,9 +24003,6 @@
       <c r="O121" t="n">
         <v>7</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.1362558261531379</v>
       </c>
@@ -24572,9 +24395,6 @@
       </c>
       <c r="O123" t="n">
         <v>8</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0.1557209441750148</v>
